--- a/artfynd/A 26259-2026 artfynd.xlsx
+++ b/artfynd/A 26259-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>114735563</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,6 +779,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114693187</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58116</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103022</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lappmes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile cinctus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>runt Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>862089</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7500452</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-05-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-05-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26259-2026 artfynd.xlsx
+++ b/artfynd/A 26259-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114735563</v>
+        <v>134752364</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>58596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pajala, Nb</t>
+          <t>Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862375</v>
+        <v>862030</v>
       </c>
       <c r="R2" t="n">
-        <v>7500054</v>
+        <v>7499326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-04-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>spår</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -775,56 +775,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Olsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114693187</v>
+        <v>114735563</v>
       </c>
       <c r="B3" t="n">
-        <v>58116</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103022</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>runt Kaunisvaara, Nb</t>
+          <t>Pajala, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862089</v>
+        <v>862375</v>
       </c>
       <c r="R3" t="n">
-        <v>7500452</v>
+        <v>7500054</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2019-04-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2019-04-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,7 +869,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -877,10 +882,1495 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134752348</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58410</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>862062</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7499928</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Via Elin Lindmark</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114693187</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58116</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103022</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lappmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile cinctus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>runt Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>862089</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7500452</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-05-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-05-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134752325</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>861940</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7500643</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134752327</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>861940</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7500642</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134752334</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>862103</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7500497</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134752338</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>862209</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7500386</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134752341</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>862106</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7500104</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134752359</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>862097</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7499585</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134752322</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58634</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103046</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gråsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Acanthis flammea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>861979</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7500631</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134752333</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58634</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103046</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gråsiska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Acanthis flammea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>862102</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7500533</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134752340</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58634</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103046</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gråsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Acanthis flammea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>862167</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7500169</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134752332</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58678</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>862058</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7500564</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134752346</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58678</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>862060</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7499928</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26259-2026 artfynd.xlsx
+++ b/artfynd/A 26259-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114735563</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752348</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114693187</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752325</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752327</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752334</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752338</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752341</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1684,6 +1729,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752359</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752364</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1907,6 +1962,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752322</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2023,6 +2083,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752333</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2139,6 +2204,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752340</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752332</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2371,8 +2446,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>